--- a/data/CAF CL.xlsx
+++ b/data/CAF CL.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Computer Science\Graduation Project\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ibram\OneDrive\Documents\GitHub\Egyptian-Premier-League-Schedule-Optimizer\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2020EC09-5F20-4CDC-8CBA-522B8D09713D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AC668159-91F8-4B2B-AF9A-0F502B4B93F4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="59" uniqueCount="18">
   <si>
     <t>Round Name</t>
   </si>
@@ -96,7 +96,7 @@
     <numFmt numFmtId="164" formatCode="dd/mm/yyyy"/>
     <numFmt numFmtId="165" formatCode="d/m/yyyy"/>
   </numFmts>
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -106,6 +106,11 @@
     <font>
       <sz val="10"/>
       <color theme="1"/>
+      <name val="Arial"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="8"/>
       <name val="Arial"/>
       <scheme val="minor"/>
     </font>
@@ -142,7 +147,22 @@
   </cellStyles>
   <dxfs count="4">
     <dxf>
-      <numFmt numFmtId="19" formatCode="m/d/yyyy"/>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="164" formatCode="dd/mm/yyyy"/>
     </dxf>
     <dxf>
       <font>
@@ -177,24 +197,9 @@
         <name val="Arial"/>
         <scheme val="minor"/>
       </font>
-      <numFmt numFmtId="164" formatCode="dd/mm/yyyy"/>
     </dxf>
     <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="Arial"/>
-        <scheme val="minor"/>
-      </font>
+      <numFmt numFmtId="19" formatCode="m/d/yyyy"/>
     </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -225,18 +230,18 @@
   <autoFilter ref="A1:B40" xr:uid="{A8BCFD28-30B8-4ADB-BEA5-9BA8CF66AC02}"/>
   <tableColumns count="2">
     <tableColumn id="1" xr3:uid="{BE92CE3D-5284-47B3-8F5B-29CC75F6BBEE}" uniqueName="1" name="Round Name" queryTableFieldId="1"/>
-    <tableColumn id="2" xr3:uid="{B9936761-FD4D-46FE-B42E-AF168E8A6757}" uniqueName="2" name="Date" queryTableFieldId="2" dataDxfId="0"/>
+    <tableColumn id="2" xr3:uid="{B9936761-FD4D-46FE-B42E-AF168E8A6757}" uniqueName="2" name="Date" queryTableFieldId="2" dataDxfId="3"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{0CC11AF7-4F1E-4DE6-AA6E-B3D10BBFA680}" name="Table1" displayName="Table1" ref="A1:B40" totalsRowShown="0" headerRowDxfId="1">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{0CC11AF7-4F1E-4DE6-AA6E-B3D10BBFA680}" name="Table1" displayName="Table1" ref="A1:B40" totalsRowShown="0" headerRowDxfId="2">
   <autoFilter ref="A1:B40" xr:uid="{0CC11AF7-4F1E-4DE6-AA6E-B3D10BBFA680}"/>
   <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{F19ED246-01D3-4BFA-91B8-F8F6B83DAD50}" name="Round Name" dataDxfId="3"/>
-    <tableColumn id="2" xr3:uid="{3783944D-3C23-42B6-AF89-F4435E16AAD4}" name="Date" dataDxfId="2"/>
+    <tableColumn id="1" xr3:uid="{F19ED246-01D3-4BFA-91B8-F8F6B83DAD50}" name="Round Name" dataDxfId="1"/>
+    <tableColumn id="2" xr3:uid="{3783944D-3C23-42B6-AF89-F4435E16AAD4}" name="Date" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -464,11 +469,17 @@
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>2</v>
+      </c>
       <c r="B3" s="4">
         <v>46251</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>2</v>
+      </c>
       <c r="B4" s="4">
         <v>46252</v>
       </c>
@@ -482,11 +493,17 @@
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>3</v>
+      </c>
       <c r="B6" s="4">
         <v>46258</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>3</v>
+      </c>
       <c r="B7" s="4">
         <v>46259</v>
       </c>
@@ -500,11 +517,17 @@
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>4</v>
+      </c>
       <c r="B9" s="4">
         <v>46279</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>4</v>
+      </c>
       <c r="B10" s="4">
         <v>46280</v>
       </c>
@@ -518,11 +541,17 @@
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>5</v>
+      </c>
       <c r="B12" s="4">
         <v>46286</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>5</v>
+      </c>
       <c r="B13" s="4">
         <v>46287</v>
       </c>
@@ -536,6 +565,9 @@
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>6</v>
+      </c>
       <c r="B15" s="4">
         <v>46353</v>
       </c>
@@ -549,11 +581,17 @@
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>7</v>
+      </c>
       <c r="B17" s="4">
         <v>46363</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>7</v>
+      </c>
       <c r="B18" s="4">
         <v>46364</v>
       </c>
@@ -567,11 +605,17 @@
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>8</v>
+      </c>
       <c r="B20" s="4">
         <v>46370</v>
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>8</v>
+      </c>
       <c r="B21" s="4">
         <v>46371</v>
       </c>
@@ -585,11 +629,17 @@
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>9</v>
+      </c>
       <c r="B23" s="4">
         <v>46391</v>
       </c>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>9</v>
+      </c>
       <c r="B24" s="4">
         <v>46392</v>
       </c>
@@ -603,11 +653,17 @@
       </c>
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>10</v>
+      </c>
       <c r="B26" s="4">
         <v>46398</v>
       </c>
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>10</v>
+      </c>
       <c r="B27" s="4">
         <v>46399</v>
       </c>
@@ -621,11 +677,17 @@
       </c>
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
+        <v>11</v>
+      </c>
       <c r="B29" s="4">
         <v>46405</v>
       </c>
     </row>
     <row r="30" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
+        <v>11</v>
+      </c>
       <c r="B30" s="4">
         <v>46406</v>
       </c>
@@ -639,6 +701,9 @@
       </c>
     </row>
     <row r="32" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A32" t="s">
+        <v>12</v>
+      </c>
       <c r="B32" s="4">
         <v>46479</v>
       </c>
@@ -652,6 +717,9 @@
       </c>
     </row>
     <row r="34" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A34" t="s">
+        <v>13</v>
+      </c>
       <c r="B34" s="4">
         <v>46486</v>
       </c>
@@ -665,6 +733,9 @@
       </c>
     </row>
     <row r="36" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A36" t="s">
+        <v>14</v>
+      </c>
       <c r="B36" s="4">
         <v>46496</v>
       </c>
@@ -678,6 +749,9 @@
       </c>
     </row>
     <row r="38" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A38" t="s">
+        <v>15</v>
+      </c>
       <c r="B38" s="4">
         <v>46503</v>
       </c>
@@ -699,6 +773,7 @@
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">
     <tablePart r:id="rId1"/>
